--- a/LearningNote/资产记录表.xlsx
+++ b/LearningNote/资产记录表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\MyKnowledgeRepository\LearningNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6DDC6A1-E62C-45BE-83A9-6D11A5D3130A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28211E0-8DFE-426C-A916-C538BD67ADB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="150">
   <si>
     <t>发工资时间</t>
   </si>
@@ -564,6 +564,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -591,6 +592,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -618,6 +620,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -645,6 +648,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -672,6 +676,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -773,6 +778,23 @@
   </si>
   <si>
     <t>发基本工资 + 股票回本2000元，目前股票亏损1万8，啥时候资金能到26万呐</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>026.4.17</t>
+    </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -796,6 +818,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -803,6 +826,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -810,12 +834,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1022,20 +1048,20 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1347,8 +1373,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表2" displayName="表2" ref="A1:L48" totalsRowShown="0">
-  <autoFilter ref="A1:L48" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表2" displayName="表2" ref="A1:L49" totalsRowShown="0">
+  <autoFilter ref="A1:L49" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="记录时间" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="中行" dataDxfId="10"/>
@@ -1791,7 +1817,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14.375" style="1" customWidth="1"/>
@@ -3636,13 +3662,50 @@
       <c r="J48" s="13">
         <v>45111.56</v>
       </c>
-      <c r="K48" s="24">
+      <c r="K48" s="10">
         <f>SUM(B48:J48)</f>
         <v>236388.14</v>
       </c>
       <c r="L48" s="17" t="s">
         <v>148</v>
       </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A49" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="B49" s="10">
+        <v>128934.17</v>
+      </c>
+      <c r="C49" s="10">
+        <v>3138.84</v>
+      </c>
+      <c r="D49" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="E49" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F49" s="10">
+        <v>0.59</v>
+      </c>
+      <c r="G49" s="10">
+        <v>65.19</v>
+      </c>
+      <c r="H49" s="10">
+        <v>0.03</v>
+      </c>
+      <c r="I49" s="13">
+        <v>58470.35</v>
+      </c>
+      <c r="J49" s="13">
+        <v>41287.160000000003</v>
+      </c>
+      <c r="K49" s="28">
+        <f>SUM(B49:J49)</f>
+        <v>231901.63000000003</v>
+      </c>
+      <c r="L49" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -3668,19 +3731,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="24" t="s">
         <v>125</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -3689,24 +3752,24 @@
       <c r="G1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="24" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="24" t="s">
         <v>131</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="24" t="s">
         <v>119</v>
       </c>
       <c r="D2" s="1">
         <v>30000</v>
       </c>
-      <c r="E2" s="25">
+      <c r="E2" s="24">
         <v>3</v>
       </c>
       <c r="F2" s="2">
@@ -3718,19 +3781,19 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="24" t="s">
         <v>131</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="24" t="s">
         <v>120</v>
       </c>
       <c r="D3" s="1">
         <v>20000</v>
       </c>
-      <c r="E3" s="25">
+      <c r="E3" s="24">
         <v>2</v>
       </c>
       <c r="F3" s="2">
@@ -3742,13 +3805,13 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="24" t="s">
         <v>131</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="24" t="s">
         <v>121</v>
       </c>
       <c r="D4" s="1">
@@ -3766,13 +3829,13 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="24" t="s">
         <v>123</v>
       </c>
       <c r="D5" s="1">
@@ -3790,13 +3853,13 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="24" t="s">
         <v>127</v>
       </c>
       <c r="D6" s="1">
@@ -3812,7 +3875,7 @@
         <f t="shared" si="0"/>
         <v>1395</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="24" t="s">
         <v>129</v>
       </c>
     </row>
@@ -3839,16 +3902,16 @@
       <c r="A1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="24" t="s">
         <v>132</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -3857,7 +3920,7 @@
       <c r="G1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="1" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3868,7 +3931,7 @@
       <c r="B2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="24" t="s">
         <v>133</v>
       </c>
       <c r="D2" s="1">
@@ -3892,7 +3955,7 @@
       <c r="B3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="24" t="s">
         <v>133</v>
       </c>
       <c r="D3" s="1">
@@ -3916,7 +3979,7 @@
       <c r="B4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="24" t="s">
         <v>133</v>
       </c>
       <c r="D4" s="1">
@@ -3940,7 +4003,7 @@
       <c r="B5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="24" t="s">
         <v>134</v>
       </c>
       <c r="D5" s="1">
@@ -3964,7 +4027,7 @@
       <c r="B6" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="24" t="s">
         <v>135</v>
       </c>
       <c r="D6" s="1">
@@ -3988,7 +4051,7 @@
       <c r="B7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="24" t="s">
         <v>136</v>
       </c>
       <c r="D7" s="1">
@@ -4012,7 +4075,7 @@
       <c r="B8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="24" t="s">
         <v>137</v>
       </c>
       <c r="D8" s="1">
@@ -4030,13 +4093,13 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="24" t="s">
         <v>140</v>
       </c>
       <c r="D9" s="1">
@@ -4045,7 +4108,7 @@
       <c r="E9" s="1">
         <v>1</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="26">
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="G9" s="1">
@@ -4054,13 +4117,13 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="24" t="s">
         <v>142</v>
       </c>
       <c r="D10" s="1">
@@ -4069,7 +4132,7 @@
       <c r="E10" s="1">
         <v>1</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="26">
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="G10" s="1">
@@ -4078,13 +4141,13 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="24" t="s">
         <v>144</v>
       </c>
       <c r="D11" s="1">
@@ -4093,7 +4156,7 @@
       <c r="E11" s="1">
         <v>1</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="26">
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="G11" s="1">
@@ -4102,13 +4165,13 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="24" t="s">
         <v>146</v>
       </c>
       <c r="D12" s="1">
@@ -4117,14 +4180,14 @@
       <c r="E12" s="1">
         <v>1</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="26">
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="H12" s="26" t="s">
+      <c r="H12" s="25" t="s">
         <v>147</v>
       </c>
     </row>

--- a/LearningNote/资产记录表.xlsx
+++ b/LearningNote/资产记录表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\MyKnowledgeRepository\LearningNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28211E0-8DFE-426C-A916-C538BD67ADB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51047DBC-E2E2-426E-A3F8-2E576B5677FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="152">
   <si>
     <t>发工资时间</t>
   </si>
@@ -795,6 +795,27 @@
       </rPr>
       <t>026.4.17</t>
     </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>026.4.20</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>母亲又给了两万给我买家私，股票却亏了两万，哎，交易纪律太差了，频繁的交易使我失去了很多，还是得耐心持股</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1373,8 +1394,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表2" displayName="表2" ref="A1:L49" totalsRowShown="0">
-  <autoFilter ref="A1:L49" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表2" displayName="表2" ref="A1:L50" totalsRowShown="0">
+  <autoFilter ref="A1:L50" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="记录时间" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="中行" dataDxfId="10"/>
@@ -1817,7 +1838,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14.375" style="1" customWidth="1"/>
@@ -3701,11 +3722,50 @@
       <c r="J49" s="13">
         <v>41287.160000000003</v>
       </c>
-      <c r="K49" s="28">
+      <c r="K49" s="10">
         <f>SUM(B49:J49)</f>
         <v>231901.63000000003</v>
       </c>
       <c r="L49" s="13"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A50" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50" s="10">
+        <v>127328.17</v>
+      </c>
+      <c r="C50" s="10">
+        <v>2642.25</v>
+      </c>
+      <c r="D50" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="E50" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F50" s="10">
+        <v>0.59</v>
+      </c>
+      <c r="G50" s="10">
+        <v>4992.09</v>
+      </c>
+      <c r="H50" s="10">
+        <v>15000.03</v>
+      </c>
+      <c r="I50" s="13">
+        <v>57599.97</v>
+      </c>
+      <c r="J50" s="13">
+        <v>40920.230000000003</v>
+      </c>
+      <c r="K50" s="28">
+        <f>SUM(B50:J50)</f>
+        <v>248488.63</v>
+      </c>
+      <c r="L50" s="13" t="s">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/LearningNote/资产记录表.xlsx
+++ b/LearningNote/资产记录表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\MyKnowledgeRepository\LearningNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51047DBC-E2E2-426E-A3F8-2E576B5677FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB3F282-1729-423D-8074-ACB5B8C0CC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="154">
   <si>
     <t>发工资时间</t>
   </si>
@@ -818,6 +818,14 @@
     <t>母亲又给了两万给我买家私，股票却亏了两万，哎，交易纪律太差了，频繁的交易使我失去了很多，还是得耐心持股</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
+  <si>
+    <t>2026.4.26</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>国信证券注入资金4万，总资金达到了9万，后续再注入1万资金，使其达到10万，做波段使用。目前亏损8500，相信自己后面会慢慢做起来的。中信证券减少资金2万，总资金达到了5万，后续再减1万，变成4万，目前亏损一万二，主要做短线为主。所以后续资金分配为国信证券10万，中信4万。</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -826,7 +834,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -903,6 +911,19 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="5">
@@ -996,7 +1017,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1081,7 +1102,13 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1394,8 +1421,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表2" displayName="表2" ref="A1:L50" totalsRowShown="0">
-  <autoFilter ref="A1:L50" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表2" displayName="表2" ref="A1:L51" totalsRowShown="0">
+  <autoFilter ref="A1:L51" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="记录时间" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="中行" dataDxfId="10"/>
@@ -1838,7 +1865,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14.375" style="1" customWidth="1"/>
@@ -3759,12 +3786,51 @@
       <c r="J50" s="13">
         <v>40920.230000000003</v>
       </c>
-      <c r="K50" s="28">
+      <c r="K50" s="10">
         <f>SUM(B50:J50)</f>
         <v>248488.63</v>
       </c>
       <c r="L50" s="13" t="s">
         <v>151</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A51" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="B51" s="29">
+        <v>107828.17</v>
+      </c>
+      <c r="C51" s="29">
+        <v>2642.25</v>
+      </c>
+      <c r="D51" s="29">
+        <v>4.2</v>
+      </c>
+      <c r="E51" s="29">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F51" s="29">
+        <v>0.59</v>
+      </c>
+      <c r="G51" s="29">
+        <v>3763.49</v>
+      </c>
+      <c r="H51" s="29">
+        <v>15001.31</v>
+      </c>
+      <c r="I51" s="28">
+        <v>38041.75</v>
+      </c>
+      <c r="J51" s="28">
+        <v>81528.39</v>
+      </c>
+      <c r="K51" s="30">
+        <f>SUM(B51:J51)</f>
+        <v>248811.25</v>
+      </c>
+      <c r="L51" s="13" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/LearningNote/资产记录表.xlsx
+++ b/LearningNote/资产记录表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\MyKnowledgeRepository\LearningNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB3F282-1729-423D-8074-ACB5B8C0CC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52124E29-A99C-4EF6-92EB-1EF64CDC3F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="158">
   <si>
     <t>发工资时间</t>
   </si>
@@ -819,11 +819,27 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>2026.4.26</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>国信证券注入资金4万，总资金达到了9万，后续再注入1万资金，使其达到10万，做波段使用。目前亏损8500，相信自己后面会慢慢做起来的。中信证券减少资金2万，总资金达到了5万，后续再减1万，变成4万，目前亏损一万二，主要做短线为主。所以后续资金分配为国信证券10万，中信4万。</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.4.25</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.4.24</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>清晨母亲又给我转了一万，真的极大减轻了我的压力！日后一定要好好报答她。今年炒股一定要挣到5万！加油！认真提升自己</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.4.27</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>买了家私，总计23980，定金付了18000。炒股的话，国信还是保持9万资金，中信5万，希望赶紧回本赚钱。</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1421,8 +1437,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表2" displayName="表2" ref="A1:L51" totalsRowShown="0">
-  <autoFilter ref="A1:L51" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表2" displayName="表2" ref="A1:L53" totalsRowShown="0">
+  <autoFilter ref="A1:L53" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="记录时间" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="中行" dataDxfId="10"/>
@@ -1865,7 +1881,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14.375" style="1" customWidth="1"/>
@@ -3633,7 +3649,7 @@
         <v>45391.21</v>
       </c>
       <c r="K46" s="10">
-        <f>SUM(B46:J46)</f>
+        <f t="shared" ref="K46:K51" si="1">SUM(B46:J46)</f>
         <v>232044.87999999998</v>
       </c>
       <c r="L46" s="17" t="s">
@@ -3672,7 +3688,7 @@
         <v>46213.36</v>
       </c>
       <c r="K47" s="10">
-        <f>SUM(B47:J47)</f>
+        <f t="shared" si="1"/>
         <v>229096.95</v>
       </c>
       <c r="L47" s="17" t="s">
@@ -3711,7 +3727,7 @@
         <v>45111.56</v>
       </c>
       <c r="K48" s="10">
-        <f>SUM(B48:J48)</f>
+        <f t="shared" si="1"/>
         <v>236388.14</v>
       </c>
       <c r="L48" s="17" t="s">
@@ -3750,7 +3766,7 @@
         <v>41287.160000000003</v>
       </c>
       <c r="K49" s="10">
-        <f>SUM(B49:J49)</f>
+        <f t="shared" si="1"/>
         <v>231901.63000000003</v>
       </c>
       <c r="L49" s="13"/>
@@ -3787,7 +3803,7 @@
         <v>40920.230000000003</v>
       </c>
       <c r="K50" s="10">
-        <f>SUM(B50:J50)</f>
+        <f t="shared" si="1"/>
         <v>248488.63</v>
       </c>
       <c r="L50" s="13" t="s">
@@ -3796,7 +3812,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A51" s="27" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B51" s="29">
         <v>107828.17</v>
@@ -3825,12 +3841,90 @@
       <c r="J51" s="28">
         <v>81528.39</v>
       </c>
-      <c r="K51" s="30">
-        <f>SUM(B51:J51)</f>
+      <c r="K51" s="29">
+        <f t="shared" si="1"/>
         <v>248811.25</v>
       </c>
       <c r="L51" s="13" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A52" s="27" t="s">
         <v>153</v>
+      </c>
+      <c r="B52" s="29">
+        <v>107828.17</v>
+      </c>
+      <c r="C52" s="29">
+        <v>2444.4699999999998</v>
+      </c>
+      <c r="D52" s="29">
+        <v>4.2</v>
+      </c>
+      <c r="E52" s="29">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F52" s="29">
+        <v>0.59</v>
+      </c>
+      <c r="G52" s="29">
+        <v>3763.49</v>
+      </c>
+      <c r="H52" s="29">
+        <v>25001.7</v>
+      </c>
+      <c r="I52" s="28">
+        <v>38041.75</v>
+      </c>
+      <c r="J52" s="28">
+        <v>81528.789999999994</v>
+      </c>
+      <c r="K52" s="29">
+        <f>SUM(B52:J52)</f>
+        <v>258614.26</v>
+      </c>
+      <c r="L52" s="13" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A53" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="B53" s="29">
+        <v>107828.17</v>
+      </c>
+      <c r="C53" s="29">
+        <v>2405.77</v>
+      </c>
+      <c r="D53" s="29">
+        <v>4.2</v>
+      </c>
+      <c r="E53" s="29">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F53" s="29">
+        <v>0.59</v>
+      </c>
+      <c r="G53" s="29">
+        <v>3221.69</v>
+      </c>
+      <c r="H53" s="29">
+        <v>7002.07</v>
+      </c>
+      <c r="I53" s="28">
+        <v>39075.46</v>
+      </c>
+      <c r="J53" s="28">
+        <v>80754.77</v>
+      </c>
+      <c r="K53" s="30">
+        <f>SUM(B53:J53)</f>
+        <v>240293.82</v>
+      </c>
+      <c r="L53" s="13" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/LearningNote/资产记录表.xlsx
+++ b/LearningNote/资产记录表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\MyKnowledgeRepository\LearningNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52124E29-A99C-4EF6-92EB-1EF64CDC3F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F27E9BEB-9425-4C13-83AD-19EDF59CD9BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="160">
   <si>
     <t>发工资时间</t>
   </si>
@@ -840,6 +840,14 @@
   </si>
   <si>
     <t>买了家私，总计23980，定金付了18000。炒股的话，国信还是保持9万资金，中信5万，希望赶紧回本赚钱。</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.4.29</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>窗帘预估费用要3500，目前交了500定金了。今天发了绩效5500左右。买了一进二的系统，花了500左右，准备研究一下，希望有成果。</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1437,8 +1445,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表2" displayName="表2" ref="A1:L53" totalsRowShown="0">
-  <autoFilter ref="A1:L53" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表2" displayName="表2" ref="A1:L54" totalsRowShown="0">
+  <autoFilter ref="A1:L54" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="记录时间" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="中行" dataDxfId="10"/>
@@ -1881,7 +1889,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14.375" style="1" customWidth="1"/>
@@ -3919,12 +3927,51 @@
       <c r="J53" s="28">
         <v>80754.77</v>
       </c>
-      <c r="K53" s="30">
+      <c r="K53" s="29">
         <f>SUM(B53:J53)</f>
         <v>240293.82</v>
       </c>
       <c r="L53" s="13" t="s">
         <v>157</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A54" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="B54" s="29">
+        <v>113339.18</v>
+      </c>
+      <c r="C54" s="29">
+        <v>1686.77</v>
+      </c>
+      <c r="D54" s="29">
+        <v>4.2</v>
+      </c>
+      <c r="E54" s="29">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F54" s="29">
+        <v>0.59</v>
+      </c>
+      <c r="G54" s="29">
+        <v>2461.48</v>
+      </c>
+      <c r="H54" s="29">
+        <v>7002.25</v>
+      </c>
+      <c r="I54" s="28">
+        <v>39008.370000000003</v>
+      </c>
+      <c r="J54" s="28">
+        <v>80866.3</v>
+      </c>
+      <c r="K54" s="30">
+        <f>SUM(B54:J54)</f>
+        <v>244370.24</v>
+      </c>
+      <c r="L54" s="13" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
